--- a/output/StructureDefinition-br-core-practitioner.xlsx
+++ b/output/StructureDefinition-br-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T10:02:10-03:00</t>
+    <t>2026-09-25T17:16:20-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-practitioner.xlsx
+++ b/output/StructureDefinition-br-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T17:16:20-03:00</t>
+    <t>2026-09-28T11:57:19-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-practitioner.xlsx
+++ b/output/StructureDefinition-br-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T11:57:19-03:00</t>
+    <t>2026-09-30T19:22:44-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-practitioner.xlsx
+++ b/output/StructureDefinition-br-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:22:44-03:00</t>
+    <t>2026-10-08T21:08:49-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-practitioner.xlsx
+++ b/output/StructureDefinition-br-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T21:08:49-03:00</t>
+    <t>2026-10-16T11:47:57-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-practitioner.xlsx
+++ b/output/StructureDefinition-br-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:47:57-03:00</t>
+    <t>2026-10-19T17:00:57-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
